--- a/data/trans_dic/POLIPATOLOGIA_2-Edad-trans_dic.xlsx
+++ b/data/trans_dic/POLIPATOLOGIA_2-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dos o más enfermedades crónicas</t>
+          <t>Población con dos o más enfermedades crónicas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,21; 3,99</t>
+          <t>1,39; 4,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,64; 4,81</t>
+          <t>1,68; 4,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,1; 5,68</t>
+          <t>2,05; 5,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,64; 18,01</t>
+          <t>6,56; 18,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,8; 10,3</t>
+          <t>5,68; 10,51</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,4; 13,25</t>
+          <t>7,28; 13,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,29; 13,14</t>
+          <t>7,03; 12,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,72; 26,43</t>
+          <t>14,19; 25,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,8; 6,47</t>
+          <t>3,75; 6,44</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,66; 7,93</t>
+          <t>4,87; 8,16</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,99; 8,39</t>
+          <t>5,04; 8,47</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,36; 19,65</t>
+          <t>11,08; 19,25</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,04; 6,14</t>
+          <t>3,05; 6,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,18; 9,15</t>
+          <t>5,08; 9,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,25; 8,47</t>
+          <t>4,06; 8,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,89; 15,32</t>
+          <t>8,02; 14,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,14; 17,96</t>
+          <t>11,9; 17,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,01; 14,46</t>
+          <t>9,09; 14,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,55; 14,98</t>
+          <t>9,58; 15,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>21,36; 58,71</t>
+          <t>21,64; 59,03</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,57; 10,75</t>
+          <t>7,74; 10,91</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,65; 10,79</t>
+          <t>7,6; 10,86</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,49; 10,78</t>
+          <t>7,46; 10,72</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,2; 42,08</t>
+          <t>16,52; 42,16</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,43; 12,13</t>
+          <t>7,41; 12,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,89; 12,62</t>
+          <t>7,69; 12,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,05; 11,76</t>
+          <t>7,19; 11,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,91; 18,14</t>
+          <t>11,55; 17,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15,68; 21,61</t>
+          <t>15,84; 21,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,29; 26,81</t>
+          <t>20,09; 26,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,84; 19,27</t>
+          <t>13,75; 19,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19,61; 29,42</t>
+          <t>18,98; 29,02</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,34; 16,19</t>
+          <t>12,5; 16,38</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14,84; 19,08</t>
+          <t>14,75; 18,99</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,85; 14,61</t>
+          <t>11,13; 14,73</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16,97; 22,76</t>
+          <t>17,26; 22,66</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,63; 19,3</t>
+          <t>13,07; 19,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,58; 20,0</t>
+          <t>13,31; 19,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,65; 25,37</t>
+          <t>18,45; 25,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,87; 31,6</t>
+          <t>10,0; 31,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>25,32; 33,24</t>
+          <t>25,68; 33,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,94; 36,89</t>
+          <t>29,51; 37,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,92; 35,73</t>
+          <t>27,93; 35,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>35,05; 45,0</t>
+          <t>34,49; 44,86</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,76; 25,14</t>
+          <t>19,87; 25,4</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22,01; 27,24</t>
+          <t>22,23; 27,78</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24,41; 29,45</t>
+          <t>24,21; 29,35</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,92; 37,08</t>
+          <t>19,46; 37,37</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>37,06; 46,99</t>
+          <t>37,11; 47,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>35,56; 45,39</t>
+          <t>35,58; 45,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32,5; 41,92</t>
+          <t>32,51; 41,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43,16; 51,22</t>
+          <t>43,04; 51,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>46,8; 56,31</t>
+          <t>46,47; 56,35</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>56,07; 65,66</t>
+          <t>55,76; 65,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,7; 59,38</t>
+          <t>49,52; 59,05</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>52,59; 59,17</t>
+          <t>52,46; 59,06</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>43,53; 50,62</t>
+          <t>43,61; 50,22</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>47,18; 54,49</t>
+          <t>47,51; 54,64</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42,29; 49,39</t>
+          <t>42,45; 49,19</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>48,54; 53,87</t>
+          <t>49,04; 54,13</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>46,76; 58,28</t>
+          <t>47,14; 58,07</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>65,49; 76,51</t>
+          <t>66,21; 76,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>51,24; 62,47</t>
+          <t>51,89; 62,15</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>53,28; 61,11</t>
+          <t>53,35; 61,07</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>67,51; 76,54</t>
+          <t>67,41; 76,75</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>71,9; 80,87</t>
+          <t>71,8; 80,94</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>65,38; 75,02</t>
+          <t>64,88; 74,66</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>70,28; 92,06</t>
+          <t>69,98; 91,31</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>59,5; 66,69</t>
+          <t>59,43; 66,59</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>70,54; 77,7</t>
+          <t>70,99; 77,98</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>60,13; 67,27</t>
+          <t>59,68; 66,92</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>63,79; 84,5</t>
+          <t>63,87; 85,02</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>62,64; 75,06</t>
+          <t>62,48; 75,48</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>76,6; 86,8</t>
+          <t>76,72; 87,22</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>67,93; 78,25</t>
+          <t>68,94; 78,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>70,67; 78,83</t>
+          <t>70,0; 78,69</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>75,75; 84,8</t>
+          <t>75,69; 84,7</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,3; 92,76</t>
+          <t>86,62; 92,96</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,13; 85,21</t>
+          <t>76,38; 85,22</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>80,64; 85,99</t>
+          <t>80,58; 85,65</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>72,57; 79,85</t>
+          <t>72,29; 79,39</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>83,9; 89,64</t>
+          <t>83,98; 89,31</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>74,52; 81,62</t>
+          <t>74,85; 81,5</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>77,47; 82,15</t>
+          <t>77,34; 81,97</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>18,39; 21,02</t>
+          <t>18,45; 21,14</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>22,97; 25,93</t>
+          <t>22,82; 25,78</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22,51; 25,31</t>
+          <t>22,39; 25,25</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24,15; 33,44</t>
+          <t>23,27; 33,35</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>31,94; 35,34</t>
+          <t>31,94; 35,21</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>37,1; 40,54</t>
+          <t>37,09; 40,54</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,45; 37,77</t>
+          <t>34,58; 37,94</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>45,36; 58,39</t>
+          <t>45,39; 58,92</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>25,53; 27,87</t>
+          <t>25,7; 27,75</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30,5; 32,73</t>
+          <t>30,49; 32,67</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28,93; 31,19</t>
+          <t>28,88; 31,12</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>36,37; 46,04</t>
+          <t>36,6; 45,61</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dos o más enfermedades crónicas</t>
+          <t>Población con dos o más enfermedades crónicas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5979; 19689</t>
+          <t>6878; 20353</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7462; 21850</t>
+          <t>7636; 21470</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8811; 23831</t>
+          <t>8614; 23600</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26540; 72021</t>
+          <t>26250; 75026</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>27099; 48148</t>
+          <t>26568; 49134</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>31846; 57023</t>
+          <t>31333; 56695</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28836; 52000</t>
+          <t>27828; 50945</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>42956; 82794</t>
+          <t>44452; 80192</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>36567; 62250</t>
+          <t>36084; 61936</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>41232; 70139</t>
+          <t>43077; 72191</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>40643; 68406</t>
+          <t>41050; 69082</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>81031; 140124</t>
+          <t>78997; 137298</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22327; 45189</t>
+          <t>22410; 45362</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>35587; 62901</t>
+          <t>34936; 62538</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25111; 50032</t>
+          <t>23952; 49180</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33422; 64902</t>
+          <t>33953; 63155</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>75962; 112308</t>
+          <t>74408; 112493</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>54965; 88224</t>
+          <t>55470; 88009</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>53845; 84398</t>
+          <t>53974; 84759</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>109366; 300670</t>
+          <t>110832; 302279</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>103038; 146314</t>
+          <t>105393; 148492</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>99190; 140017</t>
+          <t>98604; 140941</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>86380; 124366</t>
+          <t>86148; 123767</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>151537; 393685</t>
+          <t>154540; 394511</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>47457; 77479</t>
+          <t>47357; 77770</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>53827; 86049</t>
+          <t>52408; 85644</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>47170; 78713</t>
+          <t>48103; 78999</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>63858; 97280</t>
+          <t>61924; 95159</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>108155; 149087</t>
+          <t>109270; 149558</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>144223; 190614</t>
+          <t>142820; 190629</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>91530; 127427</t>
+          <t>90951; 129232</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>116081; 174184</t>
+          <t>112391; 171815</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>163886; 215076</t>
+          <t>166030; 217586</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>206678; 265714</t>
+          <t>205424; 264417</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>144312; 194363</t>
+          <t>148145; 196004</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>191481; 256783</t>
+          <t>194783; 255737</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>65553; 100208</t>
+          <t>67851; 101069</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>83454; 122902</t>
+          <t>81789; 121228</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>120508; 163874</t>
+          <t>119204; 163415</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>87630; 280567</t>
+          <t>88765; 282995</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>130538; 171419</t>
+          <t>132418; 172164</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>178348; 227345</t>
+          <t>181843; 230477</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>181246; 231886</t>
+          <t>181279; 228864</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>249847; 320786</t>
+          <t>245844; 319780</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>204489; 260156</t>
+          <t>205663; 262866</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>270890; 335219</t>
+          <t>273553; 341964</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>316125; 381451</t>
+          <t>313583; 380157</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>270835; 593493</t>
+          <t>311450; 598169</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>143325; 181703</t>
+          <t>143509; 184095</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>152720; 194913</t>
+          <t>152807; 195813</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>155316; 200365</t>
+          <t>155368; 198492</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>242248; 287442</t>
+          <t>241576; 287178</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>189051; 227501</t>
+          <t>187712; 227642</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>251097; 294028</t>
+          <t>249674; 293918</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>246914; 295020</t>
+          <t>246064; 293368</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>288131; 324198</t>
+          <t>287457; 323613</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>344206; 400259</t>
+          <t>344844; 397049</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>413883; 477967</t>
+          <t>416788; 479295</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>412249; 481478</t>
+          <t>413748; 479502</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>538342; 597469</t>
+          <t>543906; 600414</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>136803; 170510</t>
+          <t>137935; 169904</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>202864; 237018</t>
+          <t>205111; 238216</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>171318; 208864</t>
+          <t>173496; 207781</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>196176; 225004</t>
+          <t>196405; 224825</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>231522; 262486</t>
+          <t>231168; 263192</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>254540; 286270</t>
+          <t>254156; 286534</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>246964; 283396</t>
+          <t>245085; 282038</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>427535; 560085</t>
+          <t>425764; 555481</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>378152; 423815</t>
+          <t>377715; 423207</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>468242; 515783</t>
+          <t>471248; 517638</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>428160; 479023</t>
+          <t>425012; 476531</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>622963; 825125</t>
+          <t>623732; 830259</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>131463; 157536</t>
+          <t>131141; 158420</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>191374; 216862</t>
+          <t>191677; 217926</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>174576; 201091</t>
+          <t>177183; 201941</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>199839; 222888</t>
+          <t>197941; 222490</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>252925; 283153</t>
+          <t>252743; 282830</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>335688; 360829</t>
+          <t>336934; 361610</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>304647; 340969</t>
+          <t>305650; 341011</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>343390; 366168</t>
+          <t>343151; 364719</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>394643; 434219</t>
+          <t>393103; 431699</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>535948; 572659</t>
+          <t>536491; 570546</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>489709; 536404</t>
+          <t>491868; 535563</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>548962; 582076</t>
+          <t>548034; 580821</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>602418; 688582</t>
+          <t>604686; 692536</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>787129; 888717</t>
+          <t>782057; 883353</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>764151; 859191</t>
+          <t>759917; 856995</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>835717; 1156801</t>
+          <t>805141; 1153971</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1079246; 1194125</t>
+          <t>1079368; 1189882</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1320215; 1442583</t>
+          <t>1319650; 1442411</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1220979; 1338743</t>
+          <t>1225763; 1344973</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1683891; 2167780</t>
+          <t>1684866; 2187398</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1699278; 1855089</t>
+          <t>1710286; 1847148</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2130636; 2286226</t>
+          <t>2129607; 2282063</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2007492; 2164548</t>
+          <t>2004080; 2159177</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2608595; 3302182</t>
+          <t>2625165; 3271032</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/POLIPATOLOGIA_2-Edad-trans_dic.xlsx
+++ b/data/trans_dic/POLIPATOLOGIA_2-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,36%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,39; 4,12</t>
+          <t>1,22; 4,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,68; 4,73</t>
+          <t>1,68; 4,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,05; 5,63</t>
+          <t>2,09; 5,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,56; 18,76</t>
+          <t>6,42; 16,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,68; 10,51</t>
+          <t>5,68; 10,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,28; 13,18</t>
+          <t>7,31; 12,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,03; 12,87</t>
+          <t>7,13; 12,5</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14,19; 25,6</t>
+          <t>14,82; 27,56</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,75; 6,44</t>
+          <t>3,77; 6,51</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,87; 8,16</t>
+          <t>4,82; 7,88</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,04; 8,47</t>
+          <t>5,12; 8,58</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,08; 19,25</t>
+          <t>11,61; 19,41</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>16,81%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,05; 6,17</t>
+          <t>3,17; 6,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,08; 9,1</t>
+          <t>5,15; 9,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,06; 8,33</t>
+          <t>4,23; 8,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,02; 14,91</t>
+          <t>8,49; 15,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,9; 17,98</t>
+          <t>12,22; 17,96</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,09; 14,42</t>
+          <t>8,94; 14,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,58; 15,04</t>
+          <t>9,56; 14,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>21,64; 59,03</t>
+          <t>17,88; 25,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,74; 10,91</t>
+          <t>7,82; 11,07</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,6; 10,86</t>
+          <t>7,83; 10,84</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,46; 10,72</t>
+          <t>7,5; 10,83</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,52; 42,16</t>
+          <t>14,29; 19,61</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>21,16%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,41; 12,18</t>
+          <t>7,52; 11,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,69; 12,56</t>
+          <t>7,7; 12,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,19; 11,81</t>
+          <t>7,26; 11,72</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,55; 17,74</t>
+          <t>10,99; 16,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15,84; 21,68</t>
+          <t>15,62; 21,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,09; 26,82</t>
+          <t>20,22; 26,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,75; 19,54</t>
+          <t>13,67; 19,44</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,98; 29,02</t>
+          <t>25,1; 31,47</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,5; 16,38</t>
+          <t>12,33; 16,3</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14,75; 18,99</t>
+          <t>14,79; 18,95</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11,13; 14,73</t>
+          <t>11,06; 14,78</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17,26; 22,66</t>
+          <t>19,19; 23,47</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>36,85%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,07; 19,47</t>
+          <t>12,51; 19,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,31; 19,72</t>
+          <t>13,53; 19,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,45; 25,29</t>
+          <t>18,56; 25,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,0; 31,88</t>
+          <t>26,88; 34,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>25,68; 33,39</t>
+          <t>24,95; 33,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,51; 37,4</t>
+          <t>29,34; 37,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,93; 35,26</t>
+          <t>28,31; 35,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>34,49; 44,86</t>
+          <t>40,01; 45,79</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,87; 25,4</t>
+          <t>19,9; 25,03</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22,23; 27,78</t>
+          <t>22,16; 27,34</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24,21; 29,35</t>
+          <t>24,27; 29,47</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>19,46; 37,37</t>
+          <t>34,52; 39,03</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>56,42%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>51,21%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>37,11; 47,61</t>
+          <t>37,24; 47,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>35,58; 45,6</t>
+          <t>35,64; 45,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32,51; 41,53</t>
+          <t>32,55; 41,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43,04; 51,17</t>
+          <t>42,44; 50,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>46,47; 56,35</t>
+          <t>46,27; 56,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>55,76; 65,64</t>
+          <t>56,07; 66,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,52; 59,05</t>
+          <t>50,01; 59,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>52,46; 59,06</t>
+          <t>53,33; 59,4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>43,61; 50,22</t>
+          <t>43,35; 50,47</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>47,51; 54,64</t>
+          <t>47,63; 54,38</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42,45; 49,19</t>
+          <t>42,28; 49,19</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>49,04; 54,13</t>
+          <t>48,85; 53,78</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>56,98%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>64,7%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>47,14; 58,07</t>
+          <t>46,99; 58,07</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>66,21; 76,9</t>
+          <t>66,4; 77,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>51,89; 62,15</t>
+          <t>51,66; 62,34</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>53,35; 61,07</t>
+          <t>52,72; 61,03</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>67,41; 76,75</t>
+          <t>67,92; 76,81</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>71,8; 80,94</t>
+          <t>71,78; 81,24</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>64,88; 74,66</t>
+          <t>64,48; 74,44</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>69,98; 91,31</t>
+          <t>69,05; 75,39</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>59,43; 66,59</t>
+          <t>59,29; 66,61</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>70,99; 77,98</t>
+          <t>70,82; 77,77</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>59,68; 66,92</t>
+          <t>60,24; 67,61</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>63,87; 85,02</t>
+          <t>62,21; 67,3</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,75%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>62,48; 75,48</t>
+          <t>62,78; 75,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>76,72; 87,22</t>
+          <t>75,92; 86,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>68,94; 78,58</t>
+          <t>68,98; 78,96</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>70,0; 78,69</t>
+          <t>69,99; 78,71</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>75,69; 84,7</t>
+          <t>76,03; 84,7</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,62; 92,96</t>
+          <t>86,71; 92,98</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,38; 85,22</t>
+          <t>75,76; 85,28</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>80,58; 85,65</t>
+          <t>80,41; 85,61</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>72,29; 79,39</t>
+          <t>72,43; 79,72</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>83,98; 89,31</t>
+          <t>83,93; 89,66</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>74,85; 81,5</t>
+          <t>74,55; 81,42</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>77,34; 81,97</t>
+          <t>77,53; 82,26</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>39,41%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>18,45; 21,14</t>
+          <t>18,38; 21,16</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>22,82; 25,78</t>
+          <t>22,79; 25,83</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22,39; 25,25</t>
+          <t>22,38; 25,38</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23,27; 33,35</t>
+          <t>30,72; 34,11</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>31,94; 35,21</t>
+          <t>31,92; 35,19</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>37,09; 40,54</t>
+          <t>37,14; 40,32</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,58; 37,94</t>
+          <t>34,38; 37,88</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>45,39; 58,92</t>
+          <t>44,79; 47,61</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>25,7; 27,75</t>
+          <t>25,72; 27,96</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30,49; 32,67</t>
+          <t>30,53; 32,86</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28,88; 31,12</t>
+          <t>28,96; 31,24</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>36,6; 45,61</t>
+          <t>38,18; 40,53</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46589</t>
+          <t>44285</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>61139</t>
+          <t>74034</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>107728</t>
+          <t>118319</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6878; 20353</t>
+          <t>6010; 20289</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7636; 21470</t>
+          <t>7612; 21230</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8614; 23600</t>
+          <t>8752; 24653</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26250; 75026</t>
+          <t>26180; 67875</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>26568; 49134</t>
+          <t>26565; 48751</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>31333; 56695</t>
+          <t>31443; 55517</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27828; 50945</t>
+          <t>28236; 49457</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>44452; 80192</t>
+          <t>53740; 99922</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>36084; 61936</t>
+          <t>36227; 62593</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>43077; 72191</t>
+          <t>42627; 69724</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>41050; 69082</t>
+          <t>41717; 69918</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>78997; 137298</t>
+          <t>89407; 149509</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>47712</t>
+          <t>55010</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>170213</t>
+          <t>109451</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>217925</t>
+          <t>164461</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22410; 45362</t>
+          <t>23337; 44456</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34936; 62538</t>
+          <t>35378; 63446</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23952; 49180</t>
+          <t>24967; 50363</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33953; 63155</t>
+          <t>40489; 73395</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>74408; 112493</t>
+          <t>76442; 112348</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>55470; 88009</t>
+          <t>54537; 85919</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>53974; 84759</t>
+          <t>53866; 84247</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>110832; 302279</t>
+          <t>89690; 127950</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>105393; 148492</t>
+          <t>106363; 150614</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>98604; 140941</t>
+          <t>101531; 140594</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>86148; 123767</t>
+          <t>86566; 124987</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>154540; 394511</t>
+          <t>139863; 191888</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>78881</t>
+          <t>86474</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>150508</t>
+          <t>176798</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>229389</t>
+          <t>263271</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>47357; 77770</t>
+          <t>48022; 76529</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>52408; 85644</t>
+          <t>52510; 85859</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>48103; 78999</t>
+          <t>48589; 78390</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>61924; 95159</t>
+          <t>68234; 105364</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>109270; 149558</t>
+          <t>107764; 150839</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>142820; 190629</t>
+          <t>143715; 190305</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>90951; 129232</t>
+          <t>90415; 128604</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>112391; 171815</t>
+          <t>156428; 196114</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166030; 217586</t>
+          <t>163795; 216484</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>205424; 264417</t>
+          <t>206007; 263960</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>148145; 196004</t>
+          <t>147103; 196630</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>194783; 255737</t>
+          <t>238760; 292024</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>196233</t>
+          <t>211691</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>296087</t>
+          <t>317964</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>492320</t>
+          <t>529655</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>67851; 101069</t>
+          <t>64926; 99967</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>81789; 121228</t>
+          <t>83138; 121915</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>119204; 163415</t>
+          <t>119920; 165984</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>88765; 282995</t>
+          <t>188302; 239390</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>132418; 172164</t>
+          <t>128676; 171955</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>181843; 230477</t>
+          <t>180798; 231233</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>181279; 228864</t>
+          <t>183723; 232302</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>245844; 319780</t>
+          <t>294818; 337432</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>205663; 262866</t>
+          <t>205957; 258972</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>273553; 341964</t>
+          <t>272708; 336546</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>313583; 380157</t>
+          <t>314352; 381646</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>311450; 598169</t>
+          <t>496234; 561082</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>263495</t>
+          <t>280280</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>306422</t>
+          <t>343542</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>569917</t>
+          <t>623822</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>143509; 184095</t>
+          <t>144022; 182598</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>152807; 195813</t>
+          <t>153027; 196291</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>155368; 198492</t>
+          <t>155552; 200499</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>241576; 287178</t>
+          <t>258611; 304907</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>187712; 227642</t>
+          <t>186905; 226983</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>249674; 293918</t>
+          <t>251091; 296978</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>246064; 293368</t>
+          <t>248454; 293356</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>287457; 323613</t>
+          <t>324719; 361660</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>344844; 397049</t>
+          <t>342763; 399071</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>416788; 479295</t>
+          <t>417822; 477073</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>413748; 479502</t>
+          <t>412100; 479510</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>543906; 600414</t>
+          <t>595106; 655131</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>210878</t>
+          <t>231964</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>492429</t>
+          <t>315581</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>703307</t>
+          <t>547545</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>137935; 169904</t>
+          <t>137471; 169908</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>205111; 238216</t>
+          <t>205703; 238874</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>173496; 207781</t>
+          <t>172715; 208422</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>196405; 224825</t>
+          <t>214620; 248459</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>231168; 263192</t>
+          <t>232930; 263413</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>254156; 286534</t>
+          <t>254109; 287602</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>245085; 282038</t>
+          <t>243567; 281205</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>425764; 555481</t>
+          <t>303258; 331076</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>377715; 423207</t>
+          <t>376808; 423294</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>471248; 517638</t>
+          <t>470092; 516233</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>425012; 476531</t>
+          <t>428980; 481441</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>623732; 830259</t>
+          <t>526485; 569554</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>210891</t>
+          <t>231116</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>355172</t>
+          <t>386772</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>566063</t>
+          <t>617888</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>131141; 158420</t>
+          <t>131758; 158112</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>191677; 217926</t>
+          <t>189692; 215669</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>177183; 201941</t>
+          <t>177274; 202915</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>197941; 222490</t>
+          <t>217114; 244149</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>252743; 282830</t>
+          <t>253859; 282804</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>336934; 361610</t>
+          <t>337292; 361691</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>305650; 341011</t>
+          <t>303174; 341255</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>343151; 364719</t>
+          <t>373572; 397751</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>393103; 431699</t>
+          <t>393894; 433521</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>536491; 570546</t>
+          <t>536162; 572750</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>491868; 535563</t>
+          <t>489888; 535063</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>548034; 580821</t>
+          <t>600674; 637318</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1054679</t>
+          <t>1140819</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>1831969</t>
+          <t>1724142</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>2886648</t>
+          <t>2864962</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>604686; 692536</t>
+          <t>602391; 693201</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>782057; 883353</t>
+          <t>780825; 885096</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>759917; 856995</t>
+          <t>759512; 861636</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>805141; 1153971</t>
+          <t>1085220; 1205055</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1079368; 1189882</t>
+          <t>1078673; 1189146</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1319650; 1442411</t>
+          <t>1321643; 1434835</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1225763; 1344973</t>
+          <t>1218532; 1342725</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1684866; 2187398</t>
+          <t>1673647; 1779174</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1710286; 1847148</t>
+          <t>1711947; 1860969</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2129607; 2282063</t>
+          <t>2132730; 2295311</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2004080; 2159177</t>
+          <t>2009158; 2167617</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2625165; 3271032</t>
+          <t>2775215; 2946273</t>
         </is>
       </c>
     </row>
